--- a/Entrega 02/Arratia_Cobertura_mediatica_database/03_analisis_final_especies.xlsx
+++ b/Entrega 02/Arratia_Cobertura_mediatica_database/03_analisis_final_especies.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="623" documentId="8_{A44EB21C-D202-4B6E-8B3A-F64D7E198FBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F14BA19-AE91-47E4-AE85-B4164D87C57E}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{5617F6F5-E541-42D6-AF55-9597509312F3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{5617F6F5-E541-42D6-AF55-9597509312F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="3" r:id="rId1"/>
